--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_rarity_info[稀有度].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_rarity_info[稀有度].xlsx
@@ -1062,7 +1062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="20" customWidth="1" style="5" min="2" max="2"/>
@@ -1127,6 +1127,11 @@
           <t>ascend_time</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>gashapon_rate</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -1184,6 +1189,11 @@
           <t>int</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1239,6 +1249,11 @@
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>进阶所需时间(秒,按源稀有度;0为满级不可进阶)</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>孕育命中基础概率(%)</t>
         </is>
       </c>
     </row>
@@ -1286,6 +1301,9 @@
       <c r="K4" s="3" t="n">
         <v>180</v>
       </c>
+      <c r="L4" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -1331,6 +1349,9 @@
       <c r="K5" s="3" t="n">
         <v>600</v>
       </c>
+      <c r="L5" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -1376,6 +1397,9 @@
       <c r="K6" s="3" t="n">
         <v>1800</v>
       </c>
+      <c r="L6" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="3" t="n">
@@ -1421,6 +1445,9 @@
       <c r="K7" s="3" t="n">
         <v>7200</v>
       </c>
+      <c r="L7" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="3" t="n">
@@ -1466,6 +1493,9 @@
       <c r="K8" s="3" t="n">
         <v>36000</v>
       </c>
+      <c r="L8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="9" s="5">
       <c r="A9" s="3" t="n">
@@ -1511,49 +1541,55 @@
       <c r="K9" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="L9" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="3" t="n">
         <v>999</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>#1A1A22,#2A1030</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>#3A2A4D,#1C1A26</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>#4A2A5A</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>#5A1A3A</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="3" t="n">
         <v>64</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>DemonLord</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>0</v>
       </c>
     </row>
